--- a/DesignData/Excel_Masters/FamiliarStats_Master.xlsx
+++ b/DesignData/Excel_Masters/FamiliarStats_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>---</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="68">
   <si>
     <t>SummonCost</t>
   </si>
@@ -81,15 +78,157 @@
     <t>Unit.Role.Dealer</t>
   </si>
   <si>
-    <t>test1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>Cooldown</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
   <si>
     <t>AttackSpeed</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cooldown</t>
+  </si>
+  <si>
+    <t>BardFollower</t>
+  </si>
+  <si>
+    <t>Unit.Role.Tanker</t>
+  </si>
+  <si>
+    <t>CherryBee</t>
+  </si>
+  <si>
+    <t>Unit.Attack.Range</t>
+  </si>
+  <si>
+    <t>CupFelice</t>
+  </si>
+  <si>
+    <t>Dandelion</t>
+  </si>
+  <si>
+    <t>DarumaNeko</t>
+  </si>
+  <si>
+    <t>Felice</t>
+  </si>
+  <si>
+    <t>Unit.Role.Support</t>
+  </si>
+  <si>
+    <t>Firefly</t>
+  </si>
+  <si>
+    <t>ForestMacaron</t>
+  </si>
+  <si>
+    <t>ForestSpirit</t>
+  </si>
+  <si>
+    <t>Foxhound</t>
+  </si>
+  <si>
+    <t>GoldMacaron</t>
+  </si>
+  <si>
+    <t>Macaron</t>
+  </si>
+  <si>
+    <t>MageMacaron</t>
+  </si>
+  <si>
+    <t>MagicPot</t>
+  </si>
+  <si>
+    <t>MinimiNeko</t>
+  </si>
+  <si>
+    <t>Mushroom</t>
+  </si>
+  <si>
+    <t>Oowl</t>
+  </si>
+  <si>
+    <t>ShieldMacaron</t>
+  </si>
+  <si>
+    <t>Trumduck</t>
+  </si>
+  <si>
+    <t>TunerFollower</t>
+  </si>
+  <si>
+    <t>Usami</t>
+  </si>
+  <si>
+    <t>Messenger</t>
+  </si>
+  <si>
+    <t>Cannon</t>
+  </si>
+  <si>
+    <t>Fly</t>
+  </si>
+  <si>
+    <t>Golem</t>
+  </si>
+  <si>
+    <t>FelicisGuard</t>
+  </si>
+  <si>
+    <t>Clownfish</t>
+  </si>
+  <si>
+    <t>FanOfDeath</t>
+  </si>
+  <si>
+    <t>CowardTurtle</t>
+  </si>
+  <si>
+    <t>Imp</t>
+  </si>
+  <si>
+    <t>Gemini_Book</t>
+  </si>
+  <si>
+    <t>Turret</t>
+  </si>
+  <si>
+    <t>Felicis</t>
+  </si>
+  <si>
+    <t>Tacodora</t>
+  </si>
+  <si>
+    <t>KnightWolfron</t>
+  </si>
+  <si>
+    <t>Leech</t>
+  </si>
+  <si>
+    <t>NetherConnector</t>
+  </si>
+  <si>
+    <t>SmashingShrimp</t>
+  </si>
+  <si>
+    <t>ForestWolfron</t>
+  </si>
+  <si>
+    <t>Anemone</t>
+  </si>
+  <si>
+    <t>MummyMacaron</t>
+  </si>
+  <si>
+    <t>Turtlog</t>
+  </si>
+  <si>
+    <t>Bat</t>
+  </si>
+  <si>
+    <t>Mask</t>
+  </si>
+  <si>
+    <t>GuardianTreantMini</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="9.125" customWidth="1"/>
@@ -1015,84 +1154,1888 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>19</v>
       </c>
       <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2">
+        <v>0.94</v>
+      </c>
+      <c r="F2">
+        <v>150</v>
+      </c>
+      <c r="G2">
+        <v>1.4</v>
+      </c>
+      <c r="H2">
+        <v>720</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>28.8</v>
+      </c>
+      <c r="K2">
+        <v>30</v>
+      </c>
+      <c r="L2">
+        <v>600</v>
+      </c>
+      <c r="M2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>1.25</v>
+      </c>
+      <c r="F3">
+        <v>750</v>
+      </c>
+      <c r="G3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H3">
+        <v>384</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <v>48</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
+      </c>
+      <c r="L3">
+        <v>450</v>
+      </c>
+      <c r="M3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>1.05</v>
+      </c>
+      <c r="F4">
+        <v>150</v>
+      </c>
+      <c r="G4">
+        <v>1.4</v>
+      </c>
+      <c r="H4">
+        <v>480</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>48</v>
+      </c>
+      <c r="K4">
+        <v>20</v>
+      </c>
+      <c r="L4">
+        <v>600</v>
+      </c>
+      <c r="M4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>0.83</v>
+      </c>
+      <c r="F5">
+        <v>150</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>480</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>48</v>
+      </c>
+      <c r="K5">
+        <v>20</v>
+      </c>
+      <c r="L5">
+        <v>450</v>
+      </c>
+      <c r="M5">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>1.07</v>
+      </c>
+      <c r="F6">
+        <v>900</v>
+      </c>
+      <c r="G6">
+        <v>1.5</v>
+      </c>
+      <c r="H6">
+        <v>576</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>28.8</v>
+      </c>
+      <c r="K6">
+        <v>21</v>
+      </c>
+      <c r="L6">
+        <v>500</v>
+      </c>
+      <c r="M6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>0.87</v>
+      </c>
+      <c r="F7">
+        <v>750</v>
+      </c>
+      <c r="G7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H7">
+        <v>345.6</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
+        <v>33.6</v>
+      </c>
+      <c r="K7">
+        <v>14</v>
+      </c>
+      <c r="L7">
+        <v>450</v>
+      </c>
+      <c r="M7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8">
+        <v>0.88</v>
+      </c>
+      <c r="F8">
+        <v>150</v>
+      </c>
+      <c r="G8">
+        <v>1.9</v>
+      </c>
+      <c r="H8">
+        <v>720</v>
+      </c>
+      <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
+        <v>42</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>500</v>
+      </c>
+      <c r="M8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2">
+      <c r="E9">
+        <v>1.01</v>
+      </c>
+      <c r="F9">
+        <v>150</v>
+      </c>
+      <c r="G9">
+        <v>1.9</v>
+      </c>
+      <c r="H9">
+        <v>480</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>48</v>
+      </c>
+      <c r="K9">
+        <v>20</v>
+      </c>
+      <c r="L9">
+        <v>450</v>
+      </c>
+      <c r="M9">
         <v>0.1</v>
       </c>
-      <c r="F2">
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>1.06</v>
+      </c>
+      <c r="F10">
+        <v>150</v>
+      </c>
+      <c r="G10">
+        <v>1.4</v>
+      </c>
+      <c r="H10">
+        <v>480</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>48</v>
+      </c>
+      <c r="K10">
+        <v>20</v>
+      </c>
+      <c r="L10">
+        <v>550</v>
+      </c>
+      <c r="M10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F11">
+        <v>150</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>432</v>
+      </c>
+      <c r="I11">
         <v>100</v>
       </c>
-      <c r="G2">
-        <v>0.2</v>
-      </c>
-      <c r="H2">
+      <c r="J11">
+        <v>33.6</v>
+      </c>
+      <c r="K11">
+        <v>20</v>
+      </c>
+      <c r="L11">
+        <v>600</v>
+      </c>
+      <c r="M11">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="F12">
+        <v>150</v>
+      </c>
+      <c r="G12">
+        <v>1.2</v>
+      </c>
+      <c r="H12">
+        <v>800</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>60</v>
+      </c>
+      <c r="K12">
+        <v>24</v>
+      </c>
+      <c r="L12">
+        <v>550</v>
+      </c>
+      <c r="M12">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>1.28</v>
+      </c>
+      <c r="F13">
+        <v>150</v>
+      </c>
+      <c r="G13">
+        <v>2.5</v>
+      </c>
+      <c r="H13">
+        <v>480</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>48</v>
+      </c>
+      <c r="K13">
+        <v>20</v>
+      </c>
+      <c r="L13">
+        <v>600</v>
+      </c>
+      <c r="M13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14">
         <v>10</v>
       </c>
-      <c r="I2">
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14">
+        <v>1.27</v>
+      </c>
+      <c r="F14">
+        <v>150</v>
+      </c>
+      <c r="G14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H14">
+        <v>432</v>
+      </c>
+      <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
+        <v>33.6</v>
+      </c>
+      <c r="K14">
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <v>550</v>
+      </c>
+      <c r="M14">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15">
+        <v>1.18</v>
+      </c>
+      <c r="F15">
+        <v>150</v>
+      </c>
+      <c r="G15">
+        <v>1.3</v>
+      </c>
+      <c r="H15">
+        <v>480</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>48</v>
+      </c>
+      <c r="K15">
+        <v>20</v>
+      </c>
+      <c r="L15">
+        <v>600</v>
+      </c>
+      <c r="M15">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16">
+        <v>0.91</v>
+      </c>
+      <c r="F16">
+        <v>150</v>
+      </c>
+      <c r="G16">
+        <v>1.9</v>
+      </c>
+      <c r="H16">
+        <v>480</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>48</v>
+      </c>
+      <c r="K16">
+        <v>20</v>
+      </c>
+      <c r="L16">
+        <v>550</v>
+      </c>
+      <c r="M16">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="F17">
+        <v>150</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>480</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>48</v>
+      </c>
+      <c r="K17">
+        <v>20</v>
+      </c>
+      <c r="L17">
+        <v>450</v>
+      </c>
+      <c r="M17">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18">
+        <v>1.21</v>
+      </c>
+      <c r="F18">
+        <v>150</v>
+      </c>
+      <c r="G18">
+        <v>1.5</v>
+      </c>
+      <c r="H18">
+        <v>480</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>48</v>
+      </c>
+      <c r="K18">
+        <v>20</v>
+      </c>
+      <c r="L18">
+        <v>550</v>
+      </c>
+      <c r="M18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="F19">
+        <v>900</v>
+      </c>
+      <c r="G19">
+        <v>1.8</v>
+      </c>
+      <c r="H19">
+        <v>384</v>
+      </c>
+      <c r="I19">
+        <v>100</v>
+      </c>
+      <c r="J19">
+        <v>48</v>
+      </c>
+      <c r="K19">
+        <v>14</v>
+      </c>
+      <c r="L19">
+        <v>450</v>
+      </c>
+      <c r="M19">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="F20">
+        <v>900</v>
+      </c>
+      <c r="G20">
+        <v>1.5</v>
+      </c>
+      <c r="H20">
+        <v>384</v>
+      </c>
+      <c r="I20">
+        <v>100</v>
+      </c>
+      <c r="J20">
+        <v>48</v>
+      </c>
+      <c r="K20">
+        <v>14</v>
+      </c>
+      <c r="L20">
+        <v>450</v>
+      </c>
+      <c r="M20">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21">
         <v>10</v>
       </c>
-      <c r="J2">
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21">
+        <v>1.22</v>
+      </c>
+      <c r="F21">
+        <v>750</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>345.6</v>
+      </c>
+      <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
+        <v>33.6</v>
+      </c>
+      <c r="K21">
+        <v>14</v>
+      </c>
+      <c r="L21">
+        <v>600</v>
+      </c>
+      <c r="M21">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22">
+        <v>1.02</v>
+      </c>
+      <c r="F22">
+        <v>150</v>
+      </c>
+      <c r="G22">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H22">
+        <v>720</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>28.8</v>
+      </c>
+      <c r="K22">
+        <v>30</v>
+      </c>
+      <c r="L22">
+        <v>450</v>
+      </c>
+      <c r="M22">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23">
+        <v>25</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23">
+        <v>1.22</v>
+      </c>
+      <c r="F23">
+        <v>150</v>
+      </c>
+      <c r="G23">
+        <v>1.2</v>
+      </c>
+      <c r="H23">
+        <v>720</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>28.8</v>
+      </c>
+      <c r="K23">
+        <v>30</v>
+      </c>
+      <c r="L23">
+        <v>450</v>
+      </c>
+      <c r="M23">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24">
         <v>10</v>
       </c>
-      <c r="K2">
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24">
+        <v>1.17</v>
+      </c>
+      <c r="F24">
+        <v>750</v>
+      </c>
+      <c r="G24">
+        <v>1.5</v>
+      </c>
+      <c r="H24">
+        <v>345.6</v>
+      </c>
+      <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24">
+        <v>33.6</v>
+      </c>
+      <c r="K24">
+        <v>14</v>
+      </c>
+      <c r="L24">
+        <v>550</v>
+      </c>
+      <c r="M24">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25">
         <v>10</v>
       </c>
-      <c r="L2">
-        <v>1000</v>
-      </c>
-      <c r="M2">
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25">
+        <v>1.17</v>
+      </c>
+      <c r="F25">
+        <v>900</v>
+      </c>
+      <c r="G25">
+        <v>1.9</v>
+      </c>
+      <c r="H25">
+        <v>576</v>
+      </c>
+      <c r="I25">
+        <v>100</v>
+      </c>
+      <c r="J25">
+        <v>28.8</v>
+      </c>
+      <c r="K25">
+        <v>21</v>
+      </c>
+      <c r="L25">
+        <v>600</v>
+      </c>
+      <c r="M25">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="F26">
+        <v>900</v>
+      </c>
+      <c r="G26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H26">
+        <v>384</v>
+      </c>
+      <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26">
+        <v>48</v>
+      </c>
+      <c r="K26">
+        <v>14</v>
+      </c>
+      <c r="L26">
+        <v>500</v>
+      </c>
+      <c r="M26">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="F27">
+        <v>150</v>
+      </c>
+      <c r="G27">
+        <v>1.5</v>
+      </c>
+      <c r="H27">
+        <v>480</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>48</v>
+      </c>
+      <c r="K27">
+        <v>20</v>
+      </c>
+      <c r="L27">
+        <v>600</v>
+      </c>
+      <c r="M27">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28">
+        <v>10</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28">
+        <v>1.21</v>
+      </c>
+      <c r="F28">
+        <v>150</v>
+      </c>
+      <c r="G28">
+        <v>1.2</v>
+      </c>
+      <c r="H28">
+        <v>432</v>
+      </c>
+      <c r="I28">
+        <v>100</v>
+      </c>
+      <c r="J28">
+        <v>33.6</v>
+      </c>
+      <c r="K28">
+        <v>20</v>
+      </c>
+      <c r="L28">
+        <v>600</v>
+      </c>
+      <c r="M28">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29">
+        <v>15</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29">
+        <v>0.84</v>
+      </c>
+      <c r="F29">
+        <v>750</v>
+      </c>
+      <c r="G29">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H29">
+        <v>384</v>
+      </c>
+      <c r="I29">
+        <v>100</v>
+      </c>
+      <c r="J29">
+        <v>48</v>
+      </c>
+      <c r="K29">
+        <v>14</v>
+      </c>
+      <c r="L29">
+        <v>450</v>
+      </c>
+      <c r="M29">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="F30">
+        <v>600</v>
+      </c>
+      <c r="G30">
+        <v>2.1</v>
+      </c>
+      <c r="H30">
+        <v>576</v>
+      </c>
+      <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
+        <v>28.8</v>
+      </c>
+      <c r="K30">
+        <v>21</v>
+      </c>
+      <c r="L30">
+        <v>450</v>
+      </c>
+      <c r="M30">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31">
+        <v>0.97</v>
+      </c>
+      <c r="F31">
+        <v>150</v>
+      </c>
+      <c r="G31">
+        <v>1.6</v>
+      </c>
+      <c r="H31">
+        <v>432</v>
+      </c>
+      <c r="I31">
+        <v>100</v>
+      </c>
+      <c r="J31">
+        <v>33.6</v>
+      </c>
+      <c r="K31">
+        <v>20</v>
+      </c>
+      <c r="L31">
+        <v>600</v>
+      </c>
+      <c r="M31">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32">
+        <v>0.94</v>
+      </c>
+      <c r="F32">
+        <v>150</v>
+      </c>
+      <c r="G32">
+        <v>2.1</v>
+      </c>
+      <c r="H32">
+        <v>720</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>28.8</v>
+      </c>
+      <c r="K32">
+        <v>30</v>
+      </c>
+      <c r="L32">
+        <v>400</v>
+      </c>
+      <c r="M32">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33">
+        <v>1.01</v>
+      </c>
+      <c r="F33">
+        <v>150</v>
+      </c>
+      <c r="G33">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H33">
+        <v>432</v>
+      </c>
+      <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
+        <v>33.6</v>
+      </c>
+      <c r="K33">
+        <v>20</v>
+      </c>
+      <c r="L33">
+        <v>550</v>
+      </c>
+      <c r="M33">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34">
+        <v>0.95</v>
+      </c>
+      <c r="F34">
+        <v>150</v>
+      </c>
+      <c r="G34">
+        <v>2.4</v>
+      </c>
+      <c r="H34">
+        <v>720</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>28.8</v>
+      </c>
+      <c r="K34">
+        <v>30</v>
+      </c>
+      <c r="L34">
+        <v>500</v>
+      </c>
+      <c r="M34">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35">
+        <v>15</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35">
+        <v>1.3</v>
+      </c>
+      <c r="F35">
+        <v>150</v>
+      </c>
+      <c r="G35">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H35">
+        <v>480</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>48</v>
+      </c>
+      <c r="K35">
+        <v>20</v>
+      </c>
+      <c r="L35">
+        <v>450</v>
+      </c>
+      <c r="M35">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36">
+        <v>1.22</v>
+      </c>
+      <c r="F36">
+        <v>150</v>
+      </c>
+      <c r="G36">
+        <v>1.2</v>
+      </c>
+      <c r="H36">
+        <v>720</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>28.8</v>
+      </c>
+      <c r="K36">
+        <v>30</v>
+      </c>
+      <c r="L36">
+        <v>400</v>
+      </c>
+      <c r="M36">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37">
+        <v>15</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37">
+        <v>0.95</v>
+      </c>
+      <c r="F37">
+        <v>900</v>
+      </c>
+      <c r="G37">
+        <v>1.8</v>
+      </c>
+      <c r="H37">
+        <v>384</v>
+      </c>
+      <c r="I37">
+        <v>100</v>
+      </c>
+      <c r="J37">
+        <v>48</v>
+      </c>
+      <c r="K37">
+        <v>14</v>
+      </c>
+      <c r="L37">
+        <v>550</v>
+      </c>
+      <c r="M37">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38">
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F38">
+        <v>150</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38">
+        <v>432</v>
+      </c>
+      <c r="I38">
+        <v>100</v>
+      </c>
+      <c r="J38">
+        <v>33.6</v>
+      </c>
+      <c r="K38">
+        <v>20</v>
+      </c>
+      <c r="L38">
+        <v>500</v>
+      </c>
+      <c r="M38">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39">
+        <v>15</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39">
+        <v>1.2</v>
+      </c>
+      <c r="F39">
+        <v>150</v>
+      </c>
+      <c r="G39">
+        <v>1.5</v>
+      </c>
+      <c r="H39">
+        <v>480</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>48</v>
+      </c>
+      <c r="K39">
+        <v>20</v>
+      </c>
+      <c r="L39">
+        <v>450</v>
+      </c>
+      <c r="M39">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40">
+        <v>0.86</v>
+      </c>
+      <c r="F40">
+        <v>150</v>
+      </c>
+      <c r="G40">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H40">
+        <v>720</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>28.8</v>
+      </c>
+      <c r="K40">
+        <v>30</v>
+      </c>
+      <c r="L40">
+        <v>550</v>
+      </c>
+      <c r="M40">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41">
+        <v>1.27</v>
+      </c>
+      <c r="F41">
+        <v>150</v>
+      </c>
+      <c r="G41">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H41">
+        <v>720</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>28.8</v>
+      </c>
+      <c r="K41">
+        <v>30</v>
+      </c>
+      <c r="L41">
+        <v>600</v>
+      </c>
+      <c r="M41">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42">
+        <v>1.05</v>
+      </c>
+      <c r="F42">
+        <v>150</v>
+      </c>
+      <c r="G42">
+        <v>1.7</v>
+      </c>
+      <c r="H42">
+        <v>720</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>28.8</v>
+      </c>
+      <c r="K42">
+        <v>30</v>
+      </c>
+      <c r="L42">
+        <v>450</v>
+      </c>
+      <c r="M42">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43">
+        <v>10</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43">
+        <v>1.21</v>
+      </c>
+      <c r="F43">
+        <v>150</v>
+      </c>
+      <c r="G43">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H43">
+        <v>432</v>
+      </c>
+      <c r="I43">
+        <v>100</v>
+      </c>
+      <c r="J43">
+        <v>33.6</v>
+      </c>
+      <c r="K43">
+        <v>20</v>
+      </c>
+      <c r="L43">
+        <v>500</v>
+      </c>
+      <c r="M43">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44">
+        <v>25</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44">
+        <v>0.84</v>
+      </c>
+      <c r="F44">
+        <v>150</v>
+      </c>
+      <c r="G44">
+        <v>1.2</v>
+      </c>
+      <c r="H44">
+        <v>800</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>60</v>
+      </c>
+      <c r="K44">
+        <v>24</v>
+      </c>
+      <c r="L44">
+        <v>600</v>
+      </c>
+      <c r="M44">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45">
+        <v>25</v>
+      </c>
+      <c r="C45" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45">
+        <v>1.21</v>
+      </c>
+      <c r="F45">
+        <v>900</v>
+      </c>
+      <c r="G45">
+        <v>2.4</v>
+      </c>
+      <c r="H45">
+        <v>960</v>
+      </c>
+      <c r="I45">
+        <v>100</v>
+      </c>
+      <c r="J45">
+        <v>36</v>
+      </c>
+      <c r="K45">
+        <v>25.2</v>
+      </c>
+      <c r="L45">
+        <v>400</v>
+      </c>
+      <c r="M45">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46">
+        <v>25</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46">
+        <v>1.23</v>
+      </c>
+      <c r="F46">
+        <v>150</v>
+      </c>
+      <c r="G46">
+        <v>1.9</v>
+      </c>
+      <c r="H46">
+        <v>720</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>28.8</v>
+      </c>
+      <c r="K46">
+        <v>30</v>
+      </c>
+      <c r="L46">
+        <v>400</v>
+      </c>
+      <c r="M46">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -1153,23 +3096,23 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/FamiliarStats_Master.xlsx
+++ b/DesignData/Excel_Masters/FamiliarStats_Master.xlsx
@@ -5,35 +5,43 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21555" windowHeight="8040"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10710"/>
   </bookViews>
   <sheets>
-    <sheet name="FamiliarStats_Master" sheetId="1" r:id="rId1"/>
-    <sheet name="Tags" sheetId="2" r:id="rId2"/>
+    <sheet name="FamiliarStats" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="58">
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>AttackTypeTag</t>
+  </si>
+  <si>
+    <t>RoleTypeTag</t>
+  </si>
+  <si>
+    <t>RankTypeTag</t>
+  </si>
+  <si>
+    <t>BasicAttackActionHandle</t>
+  </si>
+  <si>
+    <t>PatternActionHandles</t>
+  </si>
   <si>
     <t>SummonCost</t>
   </si>
   <si>
-    <t>AttackTypeTag</t>
-  </si>
-  <si>
-    <t>RoleTypeTag</t>
-  </si>
-  <si>
-    <t>AttackRange</t>
-  </si>
-  <si>
     <t>BaseMaxHP</t>
   </si>
   <si>
@@ -52,66 +60,40 @@
     <t>BaseCritRate</t>
   </si>
   <si>
-    <t>Unit.Attack.Melee</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Tanker</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Attack.Range</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Dealer</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Support</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Attack.Melee</t>
-  </si>
-  <si>
-    <t>Unit.Role.Dealer</t>
-  </si>
-  <si>
-    <t>Cooldown</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>AttackSpeed</t>
-  </si>
-  <si>
     <t>BardFollower</t>
   </si>
   <si>
-    <t>Unit.Role.Tanker</t>
+    <t>(TagName="Unit.Attack.Melee")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Role.Tanker")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Rank.Normal")</t>
+  </si>
+  <si>
+    <t>(DataTable=None,RowName="")</t>
   </si>
   <si>
     <t>CherryBee</t>
   </si>
   <si>
-    <t>Unit.Attack.Range</t>
+    <t>(TagName="Unit.Attack.Range")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Role.Dealer")</t>
   </si>
   <si>
     <t>CupFelice</t>
   </si>
   <si>
-    <t>Dandelion</t>
-  </si>
-  <si>
     <t>DarumaNeko</t>
   </si>
   <si>
     <t>Felice</t>
   </si>
   <si>
-    <t>Unit.Role.Support</t>
+    <t>(TagName="Unit.Role.Support")</t>
   </si>
   <si>
     <t>Firefly</t>
@@ -147,15 +129,9 @@
     <t>Oowl</t>
   </si>
   <si>
-    <t>ShieldMacaron</t>
-  </si>
-  <si>
     <t>Trumduck</t>
   </si>
   <si>
-    <t>TunerFollower</t>
-  </si>
-  <si>
     <t>Usami</t>
   </si>
   <si>
@@ -186,9 +162,6 @@
     <t>Imp</t>
   </si>
   <si>
-    <t>Gemini_Book</t>
-  </si>
-  <si>
     <t>Turret</t>
   </si>
   <si>
@@ -198,9 +171,6 @@
     <t>Tacodora</t>
   </si>
   <si>
-    <t>KnightWolfron</t>
-  </si>
-  <si>
     <t>Leech</t>
   </si>
   <si>
@@ -210,9 +180,6 @@
     <t>SmashingShrimp</t>
   </si>
   <si>
-    <t>ForestWolfron</t>
-  </si>
-  <si>
     <t>Anemone</t>
   </si>
   <si>
@@ -223,9 +190,6 @@
   </si>
   <si>
     <t>Bat</t>
-  </si>
-  <si>
-    <t>Mask</t>
   </si>
   <si>
     <t>GuardianTreantMini</t>
@@ -1146,74 +1110,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="6" max="6" width="9.125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2">
-        <v>25</v>
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2">
-        <v>0.94</v>
-      </c>
-      <c r="F2">
-        <v>150</v>
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>1.4</v>
+        <v>25</v>
       </c>
       <c r="H2">
         <v>720</v>
@@ -1222,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>28.8</v>
+        <v>28.799999</v>
       </c>
       <c r="K2">
         <v>30</v>
@@ -1236,204 +1194,189 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="E3">
-        <v>1.25</v>
-      </c>
-      <c r="F3">
-        <v>750</v>
+      <c r="E3" t="s">
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>2.2999999999999998</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>384</v>
+        <v>720</v>
       </c>
       <c r="I3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>48</v>
+        <v>28.799999</v>
       </c>
       <c r="K3">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L3">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="M3">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
-        <v>15</v>
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="E4">
-        <v>1.05</v>
-      </c>
-      <c r="F4">
-        <v>150</v>
+      <c r="E4" t="s">
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>1.4</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>480</v>
+        <v>800</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L4">
         <v>600</v>
       </c>
       <c r="M4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="E5">
-        <v>0.83</v>
-      </c>
-      <c r="F5">
-        <v>150</v>
+      <c r="E5" t="s">
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>480</v>
+        <v>345.60000600000001</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>48</v>
+        <v>33.599997999999999</v>
       </c>
       <c r="K5">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L5">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="M5">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>1.07</v>
-      </c>
-      <c r="F6">
-        <v>900</v>
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>1.5</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>576</v>
+        <v>384</v>
       </c>
       <c r="I6">
         <v>100</v>
       </c>
       <c r="J6">
-        <v>28.8</v>
+        <v>48</v>
       </c>
       <c r="K6">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="M6">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7">
-        <v>0.87</v>
-      </c>
-      <c r="F7">
-        <v>750</v>
-      </c>
-      <c r="G7">
-        <v>1.1000000000000001</v>
-      </c>
       <c r="H7">
-        <v>345.6</v>
+        <v>432</v>
       </c>
       <c r="I7">
         <v>100</v>
       </c>
       <c r="J7">
-        <v>33.6</v>
+        <v>33.599997999999999</v>
       </c>
       <c r="K7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L7">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="M7">
         <v>0.05</v>
@@ -1441,40 +1384,37 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8">
-        <v>25</v>
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8">
-        <v>0.88</v>
-      </c>
-      <c r="F8">
-        <v>150</v>
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
       </c>
       <c r="G8">
-        <v>1.9</v>
+        <v>10</v>
       </c>
       <c r="H8">
-        <v>720</v>
+        <v>576</v>
       </c>
       <c r="I8">
         <v>100</v>
       </c>
       <c r="J8">
-        <v>42</v>
+        <v>28.799999</v>
       </c>
       <c r="K8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L8">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="M8">
         <v>0.05</v>
@@ -1482,25 +1422,22 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9">
         <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9">
-        <v>1.01</v>
-      </c>
-      <c r="F9">
-        <v>150</v>
-      </c>
-      <c r="G9">
-        <v>1.9</v>
       </c>
       <c r="H9">
         <v>480</v>
@@ -1515,7 +1452,7 @@
         <v>20</v>
       </c>
       <c r="L9">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="M9">
         <v>0.1</v>
@@ -1523,10 +1460,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -1534,122 +1471,113 @@
       <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="E10">
-        <v>1.06</v>
-      </c>
-      <c r="F10">
-        <v>150</v>
+      <c r="E10" t="s">
+        <v>17</v>
       </c>
       <c r="G10">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="H10">
-        <v>480</v>
+        <v>576</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>48</v>
+        <v>28.799999</v>
       </c>
       <c r="K10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L10">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="M10">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
       </c>
       <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11">
         <v>15</v>
       </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F11">
-        <v>150</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
       <c r="H11">
-        <v>432</v>
+        <v>384</v>
       </c>
       <c r="I11">
         <v>100</v>
       </c>
       <c r="J11">
-        <v>33.6</v>
+        <v>48</v>
       </c>
       <c r="K11">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L11">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="M11">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
       </c>
-      <c r="E12">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F12">
-        <v>150</v>
+      <c r="E12" t="s">
+        <v>17</v>
       </c>
       <c r="G12">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="H12">
-        <v>800</v>
+        <v>345.60000600000001</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>60</v>
+        <v>33.599997999999999</v>
       </c>
       <c r="K12">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L12">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="M12">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13">
-        <v>15</v>
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1657,122 +1585,113 @@
       <c r="D13" t="s">
         <v>16</v>
       </c>
-      <c r="E13">
-        <v>1.28</v>
-      </c>
-      <c r="F13">
-        <v>150</v>
+      <c r="E13" t="s">
+        <v>17</v>
       </c>
       <c r="G13">
-        <v>2.5</v>
+        <v>25</v>
       </c>
       <c r="H13">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>48</v>
+        <v>28.799999</v>
       </c>
       <c r="K13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L13">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M13">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14">
-        <v>10</v>
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
       </c>
       <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14">
         <v>15</v>
       </c>
-      <c r="D14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14">
-        <v>1.27</v>
-      </c>
-      <c r="F14">
-        <v>150</v>
-      </c>
-      <c r="G14">
-        <v>1.1000000000000001</v>
-      </c>
       <c r="H14">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>33.6</v>
+        <v>48</v>
       </c>
       <c r="K14">
         <v>20</v>
       </c>
       <c r="L14">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="M14">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
         <v>16</v>
       </c>
-      <c r="E15">
-        <v>1.18</v>
-      </c>
-      <c r="F15">
-        <v>150</v>
+      <c r="E15" t="s">
+        <v>17</v>
       </c>
       <c r="G15">
-        <v>1.3</v>
+        <v>25</v>
       </c>
       <c r="H15">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L15">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M15">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16">
-        <v>15</v>
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -1780,55 +1699,49 @@
       <c r="D16" t="s">
         <v>16</v>
       </c>
-      <c r="E16">
-        <v>0.91</v>
-      </c>
-      <c r="F16">
-        <v>150</v>
+      <c r="E16" t="s">
+        <v>17</v>
       </c>
       <c r="G16">
-        <v>1.9</v>
+        <v>10</v>
       </c>
       <c r="H16">
-        <v>480</v>
+        <v>576</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>48</v>
+        <v>28.799999</v>
       </c>
       <c r="K16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L16">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="M16">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17">
         <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F17">
-        <v>150</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
       </c>
       <c r="H17">
         <v>480</v>
@@ -1851,25 +1764,22 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18">
         <v>15</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18">
-        <v>1.21</v>
-      </c>
-      <c r="F18">
-        <v>150</v>
-      </c>
-      <c r="G18">
-        <v>1.5</v>
       </c>
       <c r="H18">
         <v>480</v>
@@ -1892,81 +1802,75 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19">
-        <v>15</v>
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
         <v>16</v>
       </c>
-      <c r="E19">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="F19">
-        <v>900</v>
+      <c r="E19" t="s">
+        <v>17</v>
       </c>
       <c r="G19">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="H19">
-        <v>384</v>
+        <v>432</v>
       </c>
       <c r="I19">
         <v>100</v>
       </c>
       <c r="J19">
-        <v>48</v>
+        <v>33.599997999999999</v>
       </c>
       <c r="K19">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L19">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="M19">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
         <v>16</v>
       </c>
-      <c r="E20">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="F20">
-        <v>900</v>
+      <c r="E20" t="s">
+        <v>17</v>
       </c>
       <c r="G20">
-        <v>1.5</v>
+        <v>25</v>
       </c>
       <c r="H20">
-        <v>384</v>
+        <v>800</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K20">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="L20">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="M20">
         <v>0.15</v>
@@ -1974,66 +1878,60 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21">
-        <v>10</v>
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21">
-        <v>1.22</v>
-      </c>
-      <c r="F21">
-        <v>750</v>
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>17</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H21">
-        <v>345.6</v>
+        <v>384</v>
       </c>
       <c r="I21">
         <v>100</v>
       </c>
       <c r="J21">
-        <v>33.6</v>
+        <v>48</v>
       </c>
       <c r="K21">
         <v>14</v>
       </c>
       <c r="L21">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M21">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22">
-        <v>1.02</v>
-      </c>
-      <c r="F22">
-        <v>150</v>
+        <v>16</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
       </c>
       <c r="G22">
-        <v>2.2999999999999998</v>
+        <v>25</v>
       </c>
       <c r="H22">
         <v>720</v>
@@ -2042,13 +1940,13 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>28.8</v>
+        <v>28.799999</v>
       </c>
       <c r="K22">
         <v>30</v>
       </c>
       <c r="L22">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="M22">
         <v>0.05</v>
@@ -2056,40 +1954,37 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23">
-        <v>25</v>
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23">
-        <v>1.22</v>
-      </c>
-      <c r="F23">
-        <v>150</v>
+        <v>16</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
       </c>
       <c r="G23">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="H23">
-        <v>720</v>
+        <v>432</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
-        <v>28.8</v>
+        <v>33.599997999999999</v>
       </c>
       <c r="K23">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L23">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="M23">
         <v>0.05</v>
@@ -2097,34 +1992,31 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24">
-        <v>1.17</v>
-      </c>
-      <c r="F24">
-        <v>750</v>
+        <v>16</v>
+      </c>
+      <c r="E24" t="s">
+        <v>17</v>
       </c>
       <c r="G24">
-        <v>1.5</v>
+        <v>15</v>
       </c>
       <c r="H24">
-        <v>345.6</v>
+        <v>384</v>
       </c>
       <c r="I24">
         <v>100</v>
       </c>
       <c r="J24">
-        <v>33.6</v>
+        <v>48</v>
       </c>
       <c r="K24">
         <v>14</v>
@@ -2133,112 +2025,103 @@
         <v>550</v>
       </c>
       <c r="M24">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25">
-        <v>1.17</v>
-      </c>
-      <c r="F25">
-        <v>900</v>
+        <v>16</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
       </c>
       <c r="G25">
-        <v>1.9</v>
+        <v>15</v>
       </c>
       <c r="H25">
-        <v>576</v>
+        <v>480</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>28.8</v>
+        <v>48</v>
       </c>
       <c r="K25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L25">
         <v>600</v>
       </c>
       <c r="M25">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26">
-        <v>15</v>
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
         <v>16</v>
       </c>
-      <c r="E26">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="F26">
-        <v>900</v>
+      <c r="E26" t="s">
+        <v>17</v>
       </c>
       <c r="G26">
-        <v>2.2999999999999998</v>
+        <v>10</v>
       </c>
       <c r="H26">
-        <v>384</v>
+        <v>432</v>
       </c>
       <c r="I26">
         <v>100</v>
       </c>
       <c r="J26">
-        <v>48</v>
+        <v>33.599997999999999</v>
       </c>
       <c r="K26">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L26">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="M26">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27">
+        <v>32</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27">
         <v>15</v>
-      </c>
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="F27">
-        <v>150</v>
-      </c>
-      <c r="G27">
-        <v>1.5</v>
       </c>
       <c r="H27">
         <v>480</v>
@@ -2261,40 +2144,37 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28">
-        <v>10</v>
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
       </c>
       <c r="C28" t="s">
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28">
-        <v>1.21</v>
-      </c>
-      <c r="F28">
-        <v>150</v>
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>17</v>
       </c>
       <c r="G28">
-        <v>1.2</v>
+        <v>25</v>
       </c>
       <c r="H28">
-        <v>432</v>
+        <v>720</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>33.6</v>
+        <v>28.799999</v>
       </c>
       <c r="K28">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L28">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="M28">
         <v>0.05</v>
@@ -2302,78 +2182,72 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29">
         <v>15</v>
       </c>
-      <c r="C29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29">
-        <v>0.84</v>
-      </c>
-      <c r="F29">
-        <v>750</v>
-      </c>
-      <c r="G29">
-        <v>2.2999999999999998</v>
-      </c>
       <c r="H29">
-        <v>384</v>
+        <v>480</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J29">
         <v>48</v>
       </c>
       <c r="K29">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L29">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="M29">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30">
-        <v>10</v>
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="F30">
-        <v>600</v>
+        <v>16</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
       </c>
       <c r="G30">
-        <v>2.1</v>
+        <v>25</v>
       </c>
       <c r="H30">
-        <v>576</v>
+        <v>720</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>28.8</v>
+        <v>28.799999</v>
       </c>
       <c r="K30">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L30">
         <v>450</v>
@@ -2384,81 +2258,75 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31">
-        <v>10</v>
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
       </c>
       <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31">
         <v>15</v>
       </c>
-      <c r="D31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31">
-        <v>0.97</v>
-      </c>
-      <c r="F31">
-        <v>150</v>
-      </c>
-      <c r="G31">
-        <v>1.6</v>
-      </c>
       <c r="H31">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>33.6</v>
+        <v>48</v>
       </c>
       <c r="K31">
         <v>20</v>
       </c>
       <c r="L31">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="M31">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32">
-        <v>25</v>
+        <v>51</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32">
-        <v>0.94</v>
-      </c>
-      <c r="F32">
-        <v>150</v>
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
       </c>
       <c r="G32">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="H32">
-        <v>720</v>
+        <v>432</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
-        <v>28.8</v>
+        <v>33.599997999999999</v>
       </c>
       <c r="K32">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L32">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M32">
         <v>0.05</v>
@@ -2466,34 +2334,31 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33">
-        <v>10</v>
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
       </c>
       <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33">
         <v>15</v>
       </c>
-      <c r="D33" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33">
-        <v>1.01</v>
-      </c>
-      <c r="F33">
-        <v>150</v>
-      </c>
-      <c r="G33">
-        <v>1.1000000000000001</v>
-      </c>
       <c r="H33">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>33.6</v>
+        <v>48</v>
       </c>
       <c r="K33">
         <v>20</v>
@@ -2502,71 +2367,65 @@
         <v>550</v>
       </c>
       <c r="M33">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34">
-        <v>25</v>
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
       </c>
       <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34">
         <v>15</v>
       </c>
-      <c r="D34" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34">
-        <v>0.95</v>
-      </c>
-      <c r="F34">
-        <v>150</v>
-      </c>
-      <c r="G34">
-        <v>2.4</v>
-      </c>
       <c r="H34">
-        <v>720</v>
+        <v>480</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>28.8</v>
+        <v>48</v>
       </c>
       <c r="K34">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L34">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="M34">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35">
+        <v>49</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35">
         <v>15</v>
-      </c>
-      <c r="C35" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35">
-        <v>1.3</v>
-      </c>
-      <c r="F35">
-        <v>150</v>
-      </c>
-      <c r="G35">
-        <v>2.2999999999999998</v>
       </c>
       <c r="H35">
         <v>480</v>
@@ -2589,107 +2448,98 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36">
-        <v>25</v>
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
       </c>
       <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36">
         <v>15</v>
       </c>
-      <c r="D36" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36">
-        <v>1.22</v>
-      </c>
-      <c r="F36">
-        <v>150</v>
-      </c>
-      <c r="G36">
-        <v>1.2</v>
-      </c>
       <c r="H36">
-        <v>720</v>
+        <v>384</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36">
-        <v>28.8</v>
+        <v>48</v>
       </c>
       <c r="K36">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="L36">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="M36">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>58</v>
-      </c>
-      <c r="B37">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D37" t="s">
         <v>16</v>
       </c>
-      <c r="E37">
-        <v>0.95</v>
-      </c>
-      <c r="F37">
-        <v>900</v>
+      <c r="E37" t="s">
+        <v>17</v>
       </c>
       <c r="G37">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="H37">
-        <v>384</v>
+        <v>432</v>
       </c>
       <c r="I37">
         <v>100</v>
       </c>
       <c r="J37">
-        <v>48</v>
+        <v>33.599997999999999</v>
       </c>
       <c r="K37">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L37">
         <v>550</v>
       </c>
       <c r="M37">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38">
+        <v>55</v>
+      </c>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38">
         <v>10</v>
-      </c>
-      <c r="C38" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F38">
-        <v>150</v>
-      </c>
-      <c r="G38">
-        <v>2</v>
       </c>
       <c r="H38">
         <v>432</v>
@@ -2698,7 +2548,7 @@
         <v>100</v>
       </c>
       <c r="J38">
-        <v>33.6</v>
+        <v>33.599997999999999</v>
       </c>
       <c r="K38">
         <v>20</v>
@@ -2712,10 +2562,10 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39">
-        <v>15</v>
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
       </c>
       <c r="C39" t="s">
         <v>15</v>
@@ -2723,399 +2573,35 @@
       <c r="D39" t="s">
         <v>16</v>
       </c>
-      <c r="E39">
-        <v>1.2</v>
-      </c>
-      <c r="F39">
-        <v>150</v>
+      <c r="E39" t="s">
+        <v>17</v>
       </c>
       <c r="G39">
-        <v>1.5</v>
+        <v>25</v>
       </c>
       <c r="H39">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="I39">
         <v>0</v>
       </c>
       <c r="J39">
-        <v>48</v>
+        <v>28.799999</v>
       </c>
       <c r="K39">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L39">
         <v>450</v>
       </c>
       <c r="M39">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40">
-        <v>25</v>
-      </c>
-      <c r="C40" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40">
-        <v>0.86</v>
-      </c>
-      <c r="F40">
-        <v>150</v>
-      </c>
-      <c r="G40">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H40">
-        <v>720</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>28.8</v>
-      </c>
-      <c r="K40">
-        <v>30</v>
-      </c>
-      <c r="L40">
-        <v>550</v>
-      </c>
-      <c r="M40">
         <v>0.05</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>62</v>
-      </c>
-      <c r="B41">
-        <v>25</v>
-      </c>
-      <c r="C41" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41">
-        <v>1.27</v>
-      </c>
-      <c r="F41">
-        <v>150</v>
-      </c>
-      <c r="G41">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="H41">
-        <v>720</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>28.8</v>
-      </c>
-      <c r="K41">
-        <v>30</v>
-      </c>
-      <c r="L41">
-        <v>600</v>
-      </c>
-      <c r="M41">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>63</v>
-      </c>
-      <c r="B42">
-        <v>25</v>
-      </c>
-      <c r="C42" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42">
-        <v>1.05</v>
-      </c>
-      <c r="F42">
-        <v>150</v>
-      </c>
-      <c r="G42">
-        <v>1.7</v>
-      </c>
-      <c r="H42">
-        <v>720</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>28.8</v>
-      </c>
-      <c r="K42">
-        <v>30</v>
-      </c>
-      <c r="L42">
-        <v>450</v>
-      </c>
-      <c r="M42">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>64</v>
-      </c>
-      <c r="B43">
-        <v>10</v>
-      </c>
-      <c r="C43" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43">
-        <v>1.21</v>
-      </c>
-      <c r="F43">
-        <v>150</v>
-      </c>
-      <c r="G43">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="H43">
-        <v>432</v>
-      </c>
-      <c r="I43">
-        <v>100</v>
-      </c>
-      <c r="J43">
-        <v>33.6</v>
-      </c>
-      <c r="K43">
-        <v>20</v>
-      </c>
-      <c r="L43">
-        <v>500</v>
-      </c>
-      <c r="M43">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44">
-        <v>25</v>
-      </c>
-      <c r="C44" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44">
-        <v>0.84</v>
-      </c>
-      <c r="F44">
-        <v>150</v>
-      </c>
-      <c r="G44">
-        <v>1.2</v>
-      </c>
-      <c r="H44">
-        <v>800</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>60</v>
-      </c>
-      <c r="K44">
-        <v>24</v>
-      </c>
-      <c r="L44">
-        <v>600</v>
-      </c>
-      <c r="M44">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45">
-        <v>25</v>
-      </c>
-      <c r="C45" t="s">
-        <v>23</v>
-      </c>
-      <c r="D45" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45">
-        <v>1.21</v>
-      </c>
-      <c r="F45">
-        <v>900</v>
-      </c>
-      <c r="G45">
-        <v>2.4</v>
-      </c>
-      <c r="H45">
-        <v>960</v>
-      </c>
-      <c r="I45">
-        <v>100</v>
-      </c>
-      <c r="J45">
-        <v>36</v>
-      </c>
-      <c r="K45">
-        <v>25.2</v>
-      </c>
-      <c r="L45">
-        <v>400</v>
-      </c>
-      <c r="M45">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>67</v>
-      </c>
-      <c r="B46">
-        <v>25</v>
-      </c>
-      <c r="C46" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46">
-        <v>1.23</v>
-      </c>
-      <c r="F46">
-        <v>150</v>
-      </c>
-      <c r="G46">
-        <v>1.9</v>
-      </c>
-      <c r="H46">
-        <v>720</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>28.8</v>
-      </c>
-      <c r="K46">
-        <v>30</v>
-      </c>
-      <c r="L46">
-        <v>400</v>
-      </c>
-      <c r="M46">
-        <v>0.05</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <dataValidations count="8">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="중복된 ID (RowName Error)" error="이미 존재하는 ID입니다!_x000a__x000a_RowName(행 이름)은 고유해야 합니다._x000a_(같은 이름을 두 번 쓸 수 없습니다.)" sqref="A2:A1048576">
-      <formula1>COUNTIF($A:$A, A2) &lt;= 1</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="확률 범위 오류 (0~1)" error="확률은 0.0 ~ 1.0 사이의 값만 가능합니다._x000a__x000a_[올바른 예시]_x000a_- 10% -&gt; 0.1 입력_x000a_- 50% -&gt; 0.5 입력_x000a_- 100% -&gt; 1.0 입력" sqref="M1:M1048576">
-      <formula1>0</formula1>
-      <formula2>1</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="스탯 입력 오류" error="기본 스탯은 음수(-)일 수 없습니다._x000a_0 이상의 값을 입력해주세요." sqref="I1:K1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="최소 체력 오류" error="최대 체력(MaxHP)은 최소 1 이상이어야 합니다._x000a_0을 입력하면 유닛이 생성되자마자 죽습니다!" sqref="H1:H1048576">
-      <formula1>1</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류 (Speed)" error="속도는 0보다 작을 수 없습니다._x000a_언리얼 단위(cm/s)입니다._x000a_(예: 100 = 1미터, 600 = 달리기 속도)" sqref="L1:L1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류(Range)" error="공격 사거리는 0보다 작을 수 없습니다._x000a_(예: 100 = 1미터)" sqref="F1:F1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="단위 확인 (Cooldown)" error="쿨타임은 0보다 작을 수 없습니다._x000a__x000a_※ 단위: 초 (Seconds)_x000a_- 1분 = '60' 입력_x000a_- 0.5초 = '0.5' 입력_x000a_- 쿨타임 없음 = '0' 입력_x000a__x000a_밀리초(ms) 단위가 아닙니다! 다시 확인해주세요." sqref="G2:G1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)와 0은 입력할 수 없습니다. 0 보다 큰 숫자를 입력해주세요." sqref="E2:E1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Tags!$A$1:$A$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:C1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Tags!$B$1:$B$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>D2:D1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
+  <sortState ref="A2:M39">
+    <sortCondition ref="A1"/>
+  </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DesignData/Excel_Masters/FamiliarStats_Master.xlsx
+++ b/DesignData/Excel_Masters/FamiliarStats_Master.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10710"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10035"/>
   </bookViews>
   <sheets>
     <sheet name="FamiliarStats" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="95">
   <si>
     <t>---</t>
   </si>
@@ -60,28 +60,46 @@
     <t>BaseCritRate</t>
   </si>
   <si>
+    <t>Anemone</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Attack.Melee")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Role.Tanker")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Rank.Normal")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Anemone")</t>
+  </si>
+  <si>
     <t>BardFollower</t>
   </si>
   <si>
-    <t>(TagName="Unit.Attack.Melee")</t>
-  </si>
-  <si>
-    <t>(TagName="Unit.Role.Tanker")</t>
-  </si>
-  <si>
-    <t>(TagName="Unit.Rank.Normal")</t>
-  </si>
-  <si>
-    <t>(DataTable=None,RowName="")</t>
+    <t>Bat</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Role.Dealer")</t>
+  </si>
+  <si>
+    <t>Cannon</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Attack.Range")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Role.Support")</t>
   </si>
   <si>
     <t>CherryBee</t>
   </si>
   <si>
-    <t>(TagName="Unit.Attack.Range")</t>
-  </si>
-  <si>
-    <t>(TagName="Unit.Role.Dealer")</t>
+    <t>Clownfish</t>
+  </si>
+  <si>
+    <t>CowardTurtle</t>
   </si>
   <si>
     <t>CupFelice</t>
@@ -90,15 +108,24 @@
     <t>DarumaNeko</t>
   </si>
   <si>
+    <t>FanOfDeath</t>
+  </si>
+  <si>
     <t>Felice</t>
   </si>
   <si>
-    <t>(TagName="Unit.Role.Support")</t>
+    <t>Felicis</t>
+  </si>
+  <si>
+    <t>FelicisGuard</t>
   </si>
   <si>
     <t>Firefly</t>
   </si>
   <si>
+    <t>Fly</t>
+  </si>
+  <si>
     <t>ForestMacaron</t>
   </si>
   <si>
@@ -111,6 +138,18 @@
     <t>GoldMacaron</t>
   </si>
   <si>
+    <t>Golem</t>
+  </si>
+  <si>
+    <t>GuardianTreantMini</t>
+  </si>
+  <si>
+    <t>Imp</t>
+  </si>
+  <si>
+    <t>Leech</t>
+  </si>
+  <si>
     <t>Macaron</t>
   </si>
   <si>
@@ -120,79 +159,151 @@
     <t>MagicPot</t>
   </si>
   <si>
+    <t>Messenger</t>
+  </si>
+  <si>
     <t>MinimiNeko</t>
   </si>
   <si>
+    <t>MummyMacaron</t>
+  </si>
+  <si>
     <t>Mushroom</t>
   </si>
   <si>
+    <t>NetherConnector</t>
+  </si>
+  <si>
     <t>Oowl</t>
   </si>
   <si>
+    <t>SmashingShrimp</t>
+  </si>
+  <si>
+    <t>Tacodora</t>
+  </si>
+  <si>
     <t>Trumduck</t>
   </si>
   <si>
+    <t>Turret</t>
+  </si>
+  <si>
+    <t>Turtlog</t>
+  </si>
+  <si>
     <t>Usami</t>
   </si>
   <si>
-    <t>Messenger</t>
-  </si>
-  <si>
-    <t>Cannon</t>
-  </si>
-  <si>
-    <t>Fly</t>
-  </si>
-  <si>
-    <t>Golem</t>
-  </si>
-  <si>
-    <t>FelicisGuard</t>
-  </si>
-  <si>
-    <t>Clownfish</t>
-  </si>
-  <si>
-    <t>FanOfDeath</t>
-  </si>
-  <si>
-    <t>CowardTurtle</t>
-  </si>
-  <si>
-    <t>Imp</t>
-  </si>
-  <si>
-    <t>Turret</t>
-  </si>
-  <si>
-    <t>Felicis</t>
-  </si>
-  <si>
-    <t>Tacodora</t>
-  </si>
-  <si>
-    <t>Leech</t>
-  </si>
-  <si>
-    <t>NetherConnector</t>
-  </si>
-  <si>
-    <t>SmashingShrimp</t>
-  </si>
-  <si>
-    <t>Anemone</t>
-  </si>
-  <si>
-    <t>MummyMacaron</t>
-  </si>
-  <si>
-    <t>Turtlog</t>
-  </si>
-  <si>
-    <t>Bat</t>
-  </si>
-  <si>
-    <t>GuardianTreantMini</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="BardFollower")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Bat")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Cannon")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="CherryBee")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Clownfish")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="CowardTurtle")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="CupFelice")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="DarumaNeko")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="FanOfDeath")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Felice")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Felicis")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="FelicisGuard")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Firefly")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Fly")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="ForestMacaron")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="ForestSpirit")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Foxhound")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="GoldMacaron")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Golem")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="GuardianTreantMini")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Imp")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Leech")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Macaron")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="MageMacaron")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="MagicPot")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Messenger")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="MinimiNeko")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="MummyMacaron")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Mushroom")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="NetherConnector")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Oowl")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="SmashingShrimp")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Tacodora")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Trumduck")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Turret")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Turtlog")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Familiar/DT_FamiliarBasicAttackStats.DT_FamiliarBasicAttackStats'",RowName="Usami")</t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1267,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -1194,7 +1305,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -1206,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>25</v>
@@ -1232,7 +1343,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -1244,7 +1355,7 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>25</v>
@@ -1270,19 +1381,19 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -1308,10 +1419,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -1320,7 +1431,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>15</v>
@@ -1346,19 +1457,19 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -1384,10 +1495,10 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -1396,7 +1507,7 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G8">
         <v>10</v>
@@ -1422,7 +1533,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1434,7 +1545,7 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>15</v>
@@ -1460,10 +1571,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -1472,7 +1583,7 @@
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>10</v>
@@ -1498,10 +1609,10 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -1510,7 +1621,7 @@
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>15</v>
@@ -1536,19 +1647,19 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
       <c r="D12" t="s">
         <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1574,7 +1685,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1586,7 +1697,7 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>25</v>
@@ -1612,7 +1723,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1624,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="G14">
         <v>15</v>
@@ -1650,19 +1761,19 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
         <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="G15">
         <v>25</v>
@@ -1688,10 +1799,10 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -1700,7 +1811,7 @@
         <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -1726,7 +1837,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1738,7 +1849,7 @@
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="G17">
         <v>15</v>
@@ -1764,7 +1875,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1776,7 +1887,7 @@
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="G18">
         <v>15</v>
@@ -1802,19 +1913,19 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
         <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="G19">
         <v>10</v>
@@ -1840,7 +1951,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1852,7 +1963,7 @@
         <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="G20">
         <v>25</v>
@@ -1878,10 +1989,10 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
         <v>20</v>
@@ -1890,7 +2001,7 @@
         <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="G21">
         <v>15</v>
@@ -1916,7 +2027,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1928,7 +2039,7 @@
         <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="G22">
         <v>25</v>
@@ -1954,19 +2065,19 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
         <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="G23">
         <v>10</v>
@@ -1992,10 +2103,10 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
         <v>20</v>
@@ -2004,7 +2115,7 @@
         <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="G24">
         <v>15</v>
@@ -2030,7 +2141,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -2042,7 +2153,7 @@
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="G25">
         <v>15</v>
@@ -2068,19 +2179,19 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="G26">
         <v>10</v>
@@ -2106,7 +2217,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -2118,7 +2229,7 @@
         <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="G27">
         <v>15</v>
@@ -2144,7 +2255,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -2156,7 +2267,7 @@
         <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="G28">
         <v>25</v>
@@ -2182,7 +2293,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -2194,7 +2305,7 @@
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="G29">
         <v>15</v>
@@ -2220,7 +2331,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -2232,7 +2343,7 @@
         <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="G30">
         <v>25</v>
@@ -2258,7 +2369,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -2270,7 +2381,7 @@
         <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="G31">
         <v>15</v>
@@ -2296,19 +2407,19 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
         <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -2334,7 +2445,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -2346,7 +2457,7 @@
         <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="G33">
         <v>15</v>
@@ -2384,7 +2495,7 @@
         <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="G34">
         <v>15</v>
@@ -2410,7 +2521,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2422,7 +2533,7 @@
         <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="G35">
         <v>15</v>
@@ -2448,10 +2559,10 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
         <v>20</v>
@@ -2460,7 +2571,7 @@
         <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="G36">
         <v>15</v>
@@ -2486,19 +2597,19 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D37" t="s">
         <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="G37">
         <v>10</v>
@@ -2524,19 +2635,19 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D38" t="s">
         <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="G38">
         <v>10</v>
@@ -2562,7 +2673,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2574,7 +2685,7 @@
         <v>16</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="G39">
         <v>25</v>
@@ -2599,9 +2710,6 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:M39">
-    <sortCondition ref="A1"/>
-  </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
